--- a/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt2_nucleos.xlsx
@@ -679,13 +679,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD2D02FF-2F7D-4ABC-8F39-BC12C6CCD5B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8BD3570-D4EE-483F-B45B-4F1562DE2A3B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5F27BB8-1BD1-44C3-9934-F4B5EC6419F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D907BCB7-A4F5-4670-A729-E7A16C83B6FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F6E243-F3D5-4F20-90A1-83B7AC9075E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5CBAF5E-7B10-44BD-9165-9F0CE4097889}"/>
 </file>